--- a/data/trans_dic/KIDMED_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/KIDMED_R3-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>65,67%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,47; 68,62</t>
+          <t>57,24; 78,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,96; 75,62</t>
+          <t>52,08; 74,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,33; 68,74</t>
+          <t>57,58; 74,07</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>63,41%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47,26; 64,91</t>
+          <t>58,32; 67,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,6; 66,92</t>
+          <t>59,19; 67,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,89; 64,75</t>
+          <t>60,21; 66,24</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>64,27%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,61; 69,88</t>
+          <t>57,12; 69,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55,52; 69,37</t>
+          <t>57,66; 71,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58,29; 67,85</t>
+          <t>59,55; 68,75</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>63,79%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,57; 64,55</t>
+          <t>59,91; 67,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58,54; 66,47</t>
+          <t>60,13; 66,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57,55; 64,19</t>
+          <t>61,14; 66,11</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29258</t>
+          <t>36513</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38099</t>
+          <t>28905</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67356</t>
+          <t>65418</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19047; 36848</t>
+          <t>30746; 42185</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29151; 44120</t>
+          <t>23906; 34382</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53030; 77021</t>
+          <t>57366; 73788</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>400</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>269758</t>
+          <t>296099</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>314792</t>
+          <t>268959</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>584550</t>
+          <t>565059</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>213552; 293303</t>
+          <t>272031; 316961</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>285979; 338106</t>
+          <t>251339; 284565</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>525318; 619729</t>
+          <t>536532; 590245</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>144</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>93581</t>
+          <t>106411</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>113226</t>
+          <t>95279</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>206806</t>
+          <t>201689</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82758; 102150</t>
+          <t>95211; 116467</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>100565; 125650</t>
+          <t>84844; 104672</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>190799; 222083</t>
+          <t>186882; 215765</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>584</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>392597</t>
+          <t>439023</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>466116</t>
+          <t>393143</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>858713</t>
+          <t>832165</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>342604; 420711</t>
+          <t>411473; 463185</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>435981; 495052</t>
+          <t>371438; 411937</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>803647; 896420</t>
+          <t>797550; 862427</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/KIDMED_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/KIDMED_R3-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que tienen una alta adherencia a la dieta mediterránea (tasa de respuesta: 96,61%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>67,98%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>62,97%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>65,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>57,24; 78,54</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>52,08; 74,9</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>57,58; 74,07</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>63,48%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>63,33%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>63,41%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>58,32; 67,96</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>59,19; 67,01</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>60,21; 66,24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>63,84%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>64,75%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>64,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>57,12; 69,87</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>57,66; 71,14</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>59,55; 68,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>63,92%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>63,65%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>63,79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>59,91; 67,44</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>60,13; 66,69</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>61,14; 66,11</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.6797513442537666</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.6296701033170278</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.6566738514007461</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>36513</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>28905</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>65418</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.5723836180763737</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.5207765841101824</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.575844783819658</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>30746; 42185</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>23906; 34382</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57366; 73788</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.7853542302206072</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.7489787837657836</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.7406908108398761</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>814</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.6348294381178081</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.633342323157458</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.6341207241375322</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>296099</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>268959</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>565059</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.5832273865104562</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.5918513166918156</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.6021070066674372</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>272031; 316961</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>251339; 284565</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>536532; 590245</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.6795575559513247</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.670092019818385</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.6623849226694604</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.6383907319715076</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.6475377767373161</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.6426794032627442</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>106411</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>95279</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>201689</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.5711981695094144</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.5766188810170904</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.5954983497878706</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>95211; 116467</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>84844; 104672</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>186882; 215765</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.6987203001916643</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.711375616631391</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.6875328363091568</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1197</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.639206958141206</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.6364508040325676</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.6379018900391231</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>439023</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>393143</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>832165</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.5990956357256126</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.6013130895132114</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.6113671275731317</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>411473; 463185</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>371438; 411937</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>797550; 862427</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.674386325971589</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.666875960560846</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.661099435583088</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen una alta adherencia a la dieta mediterránea (tasa de respuesta: 96,61%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>36513</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>28905</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>65418</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>30746</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>23906</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>57366</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>42185</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>34382</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>73788</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>414</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>296099</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>268959</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>565059</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>272031</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>251339</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>536532</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>316961</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>284565</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>590245</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>147</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>144</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>106411</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>95279</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>201689</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>95211</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>84844</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>186882</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>116467</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>104672</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>215765</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>613</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>584</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>439023</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>393143</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>832165</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>411473</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>371438</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>797550</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>463185</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>411937</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>862427</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>